--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487038_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487038_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.962</v>
+        <v>4.9408</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7876</v>
+        <v>4.686</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1744</v>
+        <v>0.2547</v>
       </c>
       <c r="G2" t="n">
         <v>4.8289</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5963</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8376</v>
+        <v>0.736</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2413</v>
+        <v>-0.161</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6562</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>J. JORGE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3823</v>
+        <v>0.3308</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1008</v>
+        <v>-1.4962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2816</v>
+        <v>1.827</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.8355</v>
+        <v>0.6051</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.7573</v>
+        <v>-0.9822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9218</v>
+        <v>1.5873</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0751</v>
+        <v>1.0052</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.8891</v>
+        <v>0.4604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.5448</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7604</v>
+        <v>-0.4001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8682</v>
+        <v>-1.4426</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1078</v>
+        <v>1.0424</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3161</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3511</v>
+        <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5387</v>
+        <v>-0.3745</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5619</v>
+        <v>-0.1854</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0232</v>
+        <v>-0.1891</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3281</v>
+        <v>-0.2859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2859</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G4" t="n">
         <v>0.1335</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JORGE RODRIGUEZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6022</v>
+        <v>-0.3672</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.8576</v>
+        <v>-0.1402</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2553</v>
+        <v>-0.227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6051</v>
+        <v>-1.8355</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9822</v>
+        <v>-2.7573</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5873</v>
+        <v>0.9218</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0052</v>
+        <v>-1.0751</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4604</v>
+        <v>-1.8891</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5448</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4001</v>
+        <v>-0.7604</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4426</v>
+        <v>-0.8682</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0424</v>
+        <v>0.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3161</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7021</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3075</v>
+        <v>-0.2109</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5467</v>
+        <v>0.3209</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2392</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RUIZ RUIZ</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9151</v>
+        <v>-0.5644</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4455</v>
+        <v>2.2924</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4696</v>
+        <v>-2.8568</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3587</v>
+        <v>2.2649</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3332</v>
+        <v>0.5991</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6919</v>
+        <v>1.6658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7126</v>
+        <v>3.4061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>1.9817</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6919</v>
+        <v>1.4245</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3539</v>
+        <v>-1.1412</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3539</v>
+        <v>-1.3825</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.2413</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.158</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1157</v>
+        <v>-0.3781</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1977</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1157</v>
+        <v>-0.5758</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.7418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>D. RUIZ RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.957</v>
+        <v>-0.7882</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6321</v>
+        <v>-0.3453</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5891</v>
+        <v>-0.4428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2649</v>
+        <v>0.3587</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5991</v>
+        <v>-0.3332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6658</v>
+        <v>0.6919</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4061</v>
+        <v>0.7126</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9817</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4245</v>
+        <v>0.6919</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1412</v>
+        <v>-0.3539</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3825</v>
+        <v>-0.3539</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2413</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0532</v>
+        <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9301</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.0112</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4627</v>
+        <v>0.1001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3081</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6477</v>
+        <v>-1.1599</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8796</v>
+        <v>-0.5792</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7681</v>
+        <v>-0.5807</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8295</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.1448</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3569</v>
+        <v>-0.0565</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2756</v>
+        <v>-0.0883</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5717</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3584</v>
+        <v>-1.7774</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5023</v>
+        <v>-0.2425</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8562</v>
+        <v>-1.5349</v>
       </c>
       <c r="G9" t="n">
         <v>0.355</v>
@@ -1156,13 +1156,13 @@
         <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5084</v>
+        <v>-0.9274</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0925</v>
+        <v>0.1673</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4159</v>
+        <v>-1.0946</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1701</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4759</v>
+        <v>-5.3031</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1499</v>
+        <v>-4.4529</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.326</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8183</v>
+        <v>-1.0949</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7126</v>
+        <v>0.9679</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1057</v>
+        <v>-2.0628</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5512</v>
+        <v>-0.0342</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2566</v>
+        <v>1.8629</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2945</v>
+        <v>-1.8971</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2672</v>
+        <v>-1.0607</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.456</v>
+        <v>-0.8951</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1888</v>
+        <v>-0.1657</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4741</v>
+        <v>-4.2462</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8865</v>
+        <v>-1.3131</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8754</v>
+        <v>-0.1725</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9889</v>
+        <v>-1.1406</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.365</v>
+        <v>-6.0177</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1132</v>
+        <v>-5.8523</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2518</v>
+        <v>-0.1653</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0949</v>
+        <v>-3.8183</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9679</v>
+        <v>-3.7126</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0628</v>
+        <v>-0.1057</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0342</v>
+        <v>-3.5512</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8629</v>
+        <v>-2.2566</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8971</v>
+        <v>-1.2945</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0607</v>
+        <v>-0.2672</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8951</v>
+        <v>-1.456</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1657</v>
+        <v>1.1888</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.2462</v>
+        <v>-3.4741</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3749</v>
+        <v>0.3447</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8328</v>
+        <v>1.173</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5421</v>
+        <v>-0.8283</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.8256</v>
+        <v>-10.5282</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.427599999999999</v>
+        <v>-6.130199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.398099999999999</v>
+        <v>-4.398</v>
       </c>
       <c r="G12" t="n">
         <v>0.9679000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.705299999999999</v>
+        <v>-3.7053</v>
       </c>
       <c r="I12" t="n">
         <v>4.673299999999999</v>
@@ -1366,7 +1366,7 @@
         <v>6.939399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5.4114</v>
+        <v>5.411399999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1.528199999999999</v>
@@ -1390,10 +1390,10 @@
         <v>13.5107</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6705</v>
+        <v>-2.3732</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9833</v>
+        <v>2.2806</v>
       </c>
       <c r="U12" t="n">
         <v>-4.6538</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.7036</v>
+        <v>7.1886</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5521</v>
+        <v>4.8497</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1515</v>
+        <v>2.3389</v>
       </c>
       <c r="G13" t="n">
         <v>3.564</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5183</v>
+        <v>0.0033</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2672</v>
+        <v>0.5649</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7489</v>
+        <v>-0.5615</v>
       </c>
       <c r="V13" t="n">
         <v>1.8842</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.593</v>
+        <v>3.0658</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0833</v>
+        <v>2.7743</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4903</v>
+        <v>0.2916</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4996</v>
+        <v>1.5522</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9801</v>
+        <v>1.8256</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4805</v>
+        <v>-0.2735</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3895</v>
+        <v>1.8991</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4308</v>
+        <v>1.8991</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0414</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8898</v>
+        <v>-0.3469</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4507</v>
+        <v>-0.0735</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4391</v>
+        <v>-0.2735</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2811</v>
+        <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3756</v>
+        <v>0.7416</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4153</v>
+        <v>0.8752</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0397</v>
+        <v>-0.1335</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5983</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0658</v>
+        <v>2.7522</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7743</v>
+        <v>4.0819</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2916</v>
+        <v>-1.3297</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5522</v>
+        <v>0.4996</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8256</v>
+        <v>0.9801</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2735</v>
+        <v>-0.4805</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8991</v>
+        <v>3.3895</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8991</v>
+        <v>3.4308</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.0414</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3469</v>
+        <v>-2.8898</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0735</v>
+        <v>-2.4507</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2735</v>
+        <v>-0.4391</v>
       </c>
       <c r="P15" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7416</v>
+        <v>1.5348</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8752</v>
+        <v>1.4139</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1335</v>
+        <v>0.1209</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.5983</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2436</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5118</v>
+        <v>2.5093</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0002</v>
+        <v>1.174</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5116</v>
+        <v>1.3353</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8046</v>
+        <v>2.2494</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1822</v>
+        <v>1.274</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9868</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2304</v>
+        <v>1.3084</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5022</v>
+        <v>1.2677</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7326</v>
+        <v>0.0407</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5742</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.32</v>
+        <v>0.0064</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2542</v>
+        <v>0.9346</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6723</v>
+        <v>-0.582</v>
       </c>
       <c r="T16" t="n">
-        <v>1.437</v>
+        <v>-0.3321</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2353</v>
+        <v>-0.2499</v>
       </c>
       <c r="V16" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>2.1278</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3298</v>
+        <v>1.79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6733</v>
+        <v>-0.4003</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6566</v>
+        <v>2.1904</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2494</v>
+        <v>0.8046</v>
       </c>
       <c r="H17" t="n">
-        <v>1.274</v>
+        <v>-0.1822</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9868</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3084</v>
+        <v>0.2304</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2677</v>
+        <v>-0.5022</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>0.7326</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.5742</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0064</v>
+        <v>0.32</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9346</v>
+        <v>0.2542</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7615</v>
+        <v>0.9505</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8328</v>
+        <v>1.0365</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0713</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="V17" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.228</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.1278</v>
-      </c>
       <c r="X17" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1942</v>
+        <v>0.2735</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3307</v>
+        <v>0.0698</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5249</v>
+        <v>0.2037</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2869</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0251</v>
+        <v>0.1044</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.501</v>
+        <v>0.1798</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0183</v>
+        <v>0.1002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5914</v>
+        <v>-1.6537</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6098</v>
+        <v>1.7539</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7758</v>
+        <v>-0.868</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4959</v>
+        <v>-0.2411</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2717</v>
+        <v>-0.6269</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5187</v>
+        <v>-1.8224</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0971</v>
+        <v>-0.5279</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5783</v>
+        <v>-1.2945</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2945</v>
+        <v>0.9544</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6012</v>
+        <v>0.2868</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6933</v>
+        <v>0.6676</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2076</v>
+        <v>-0.3599</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0727</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2803</v>
+        <v>-0.2657</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5523</v>
+        <v>-0.0183</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2191</v>
+        <v>0.5914</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7714</v>
+        <v>-0.6098</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2199</v>
+        <v>-0.7758</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1952</v>
+        <v>0.4959</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9752999999999999</v>
+        <v>-1.2717</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0321</v>
+        <v>0.5187</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2938</v>
+        <v>1.0971</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2617</v>
+        <v>-0.5783</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1878</v>
+        <v>-1.2945</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9014</v>
+        <v>-0.6012</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2863</v>
+        <v>-0.6933</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4746</v>
+        <v>-0.2076</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2512</v>
+        <v>0.0727</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2234</v>
+        <v>-0.2803</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7217</v>
+        <v>-0.6524</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1544</v>
+        <v>0.1189</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4326</v>
+        <v>-0.7714</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.868</v>
+        <v>-1.2199</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2411</v>
+        <v>-2.1952</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6269</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8224</v>
+        <v>-0.0321</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5279</v>
+        <v>-1.2938</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2945</v>
+        <v>1.2617</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9544</v>
+        <v>-1.1878</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2868</v>
+        <v>-0.9014</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6676</v>
+        <v>-0.2863</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1818</v>
+        <v>0.3745</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>0.151</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.587</v>
+        <v>0.2234</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5053</v>
+        <v>-2.8311</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0779</v>
+        <v>-2.3769</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4275</v>
+        <v>-0.4543</v>
       </c>
       <c r="G22" t="n">
         <v>-3.547</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3444</v>
+        <v>0.3298</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0766</v>
+        <v>0.6243</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2677</v>
+        <v>-0.2945</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7749</v>
+        <v>-3.3521</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9326</v>
+        <v>-4.8311</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1577</v>
+        <v>1.4789</v>
       </c>
       <c r="G23" t="n">
         <v>-2.94</v>
@@ -2248,13 +2248,13 @@
         <v>2.7021</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6419</v>
+        <v>-0.2191</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6848</v>
+        <v>0.4168</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9571</v>
+        <v>-0.6359</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>10.8257</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3981</v>
+        <v>4.398000000000002</v>
       </c>
       <c r="F24" t="n">
         <v>6.4275</v>
@@ -2302,13 +2302,13 @@
         <v>5.972000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>9.116999999999999</v>
+        <v>9.117000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-3.145</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.9395</v>
+        <v>-6.939500000000001</v>
       </c>
       <c r="N24" t="n">
         <v>-5.4114</v>
@@ -2317,7 +2317,7 @@
         <v>-1.528</v>
       </c>
       <c r="P24" t="n">
-        <v>4.825200000000001</v>
+        <v>4.8252</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.5105</v>
@@ -2329,7 +2329,7 @@
         <v>2.6703</v>
       </c>
       <c r="T24" t="n">
-        <v>4.653599999999999</v>
+        <v>4.6537</v>
       </c>
       <c r="U24" t="n">
         <v>-1.9832</v>
